--- a/LeaguePost/league_team_02.xlsx
+++ b/LeaguePost/league_team_02.xlsx
@@ -64,6 +64,48 @@
     <t>kaiho</t>
   </si>
   <si>
+    <t>島根大学</t>
+  </si>
+  <si>
+    <t>島根大</t>
+  </si>
+  <si>
+    <t>島根県</t>
+  </si>
+  <si>
+    <t>shimadai</t>
+  </si>
+  <si>
+    <t>広島大学</t>
+  </si>
+  <si>
+    <t>広島大</t>
+  </si>
+  <si>
+    <t>hirodai</t>
+  </si>
+  <si>
+    <t>岡山大学医学部</t>
+  </si>
+  <si>
+    <t>岡大医</t>
+  </si>
+  <si>
+    <t>岡山県</t>
+  </si>
+  <si>
+    <t>okai</t>
+  </si>
+  <si>
+    <t>吉備国際大学</t>
+  </si>
+  <si>
+    <t>吉備国</t>
+  </si>
+  <si>
+    <t>kibikoku</t>
+  </si>
+  <si>
     <t>鳥取大学</t>
   </si>
   <si>
@@ -74,48 +116,6 @@
   </si>
   <si>
     <t>toridai</t>
-  </si>
-  <si>
-    <t>広島大学</t>
-  </si>
-  <si>
-    <t>広島大</t>
-  </si>
-  <si>
-    <t>hirodai</t>
-  </si>
-  <si>
-    <t>岡山大学医学部</t>
-  </si>
-  <si>
-    <t>岡大医</t>
-  </si>
-  <si>
-    <t>岡山県</t>
-  </si>
-  <si>
-    <t>okai</t>
-  </si>
-  <si>
-    <t>吉備国際大学</t>
-  </si>
-  <si>
-    <t>吉備国</t>
-  </si>
-  <si>
-    <t>kibikoku</t>
-  </si>
-  <si>
-    <t>島根大学</t>
-  </si>
-  <si>
-    <t>島根大</t>
-  </si>
-  <si>
-    <t>島根県</t>
-  </si>
-  <si>
-    <t>shimadai</t>
   </si>
   <si>
     <t>川崎医科大学</t>
